--- a/data/trans_dic/P1418-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1418-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 13,25</t>
+          <t>9,44; 13,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,94</t>
+          <t>6,33; 9,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,2</t>
+          <t>4,77; 8,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,05; 14,77</t>
+          <t>9,34; 14,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 20,24</t>
+          <t>16,07; 20,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,45; 20,67</t>
+          <t>16,56; 20,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 17,61</t>
+          <t>13,09; 17,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 22,61</t>
+          <t>17,48; 21,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,64; 16,56</t>
+          <t>13,64; 16,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 15,69</t>
+          <t>12,72; 15,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,12</t>
+          <t>9,97; 13,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 18,85</t>
+          <t>14,88; 17,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,87</t>
+          <t>2,25; 3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,93</t>
+          <t>0,77; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,15</t>
+          <t>1,02; 2,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,66</t>
+          <t>2,4; 4,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,75</t>
+          <t>4,41; 6,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,3</t>
+          <t>4,04; 6,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,46</t>
+          <t>3,47; 5,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,5</t>
+          <t>5,32; 6,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,92</t>
+          <t>3,53; 4,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,67</t>
+          <t>2,4; 3,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,47</t>
+          <t>2,4; 3,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,73</t>
+          <t>4,07; 5,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,27</t>
+          <t>1,42; 4,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,57</t>
+          <t>0,4; 2,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,95</t>
+          <t>0,2; 2,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,97</t>
+          <t>0,89; 2,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,15</t>
+          <t>2,42; 6,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,73</t>
+          <t>0,93; 3,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,26</t>
+          <t>1,33; 4,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,45</t>
+          <t>3,55; 6,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,66</t>
+          <t>2,34; 4,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,5</t>
+          <t>0,82; 2,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,54</t>
+          <t>0,92; 2,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,23</t>
+          <t>2,43; 4,16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,28</t>
+          <t>4,76; 6,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,71</t>
+          <t>2,61; 3,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,92</t>
+          <t>1,93; 3,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,69</t>
+          <t>3,67; 4,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 11,28</t>
+          <t>9,16; 11,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 10,82</t>
+          <t>8,78; 10,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 8,14</t>
+          <t>6,28; 8,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,36</t>
+          <t>8,08; 9,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,48</t>
+          <t>7,14; 8,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,11</t>
+          <t>5,89; 7,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,39</t>
+          <t>4,29; 5,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,83</t>
+          <t>6,08; 7,09</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>67091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>150721</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>213772</t>
+          <t>227355</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97284; 136676</t>
+          <t>97375; 136973</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62373; 96889</t>
+          <t>61713; 96826</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37036; 61891</t>
+          <t>36001; 62409</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51525; 75715</t>
+          <t>53787; 81238</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>208381; 266242</t>
+          <t>211291; 268983</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>220080; 276523</t>
+          <t>221524; 280791</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>127883; 175114</t>
+          <t>130229; 177618</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>135260; 170037</t>
+          <t>143349; 178381</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>320086; 388749</t>
+          <t>320097; 386697</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>292656; 362882</t>
+          <t>294232; 362927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169663; 229495</t>
+          <t>174429; 227768</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>194607; 238415</t>
+          <t>207703; 249654</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64004</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>120422</t>
+          <t>132770</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>184426</t>
+          <t>202279</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37008; 65487</t>
+          <t>38179; 65919</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15318; 37881</t>
+          <t>15214; 36821</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21209; 44602</t>
+          <t>21113; 43367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43789; 83822</t>
+          <t>53573; 89241</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67587; 107219</t>
+          <t>69968; 106539</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69692; 110509</t>
+          <t>70899; 110738</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69879; 108596</t>
+          <t>69020; 107262</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88737; 145269</t>
+          <t>115209; 151441</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>114339; 161541</t>
+          <t>115701; 161343</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90265; 136300</t>
+          <t>89285; 134688</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96107; 140844</t>
+          <t>97434; 143713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>140285; 213728</t>
+          <t>178717; 229208</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41265</t>
+          <t>45967</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7056; 23543</t>
+          <t>7828; 22864</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1015; 12363</t>
+          <t>1902; 13203</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1106; 10688</t>
+          <t>1117; 11207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6079; 19191</t>
+          <t>6351; 18625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11301; 29288</t>
+          <t>11520; 29884</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4641; 17094</t>
+          <t>4275; 17772</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7022; 23403</t>
+          <t>7301; 23553</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21430; 42484</t>
+          <t>25986; 47064</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22670; 47925</t>
+          <t>24022; 47242</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8128; 23477</t>
+          <t>7726; 23980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10236; 27836</t>
+          <t>10127; 28882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30528; 55221</t>
+          <t>35089; 60091</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138127</t>
+          <t>148039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>301337</t>
+          <t>327560</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>439464</t>
+          <t>475600</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>154201; 205646</t>
+          <t>156040; 206738</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87666; 126829</t>
+          <t>89125; 131487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64721; 98679</t>
+          <t>65059; 101400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107278; 161699</t>
+          <t>128878; 173553</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>308880; 381226</t>
+          <t>309379; 378888</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>310294; 383963</t>
+          <t>311549; 384223</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>223789; 287592</t>
+          <t>221657; 286312</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>247151; 340983</t>
+          <t>300544; 354285</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>482505; 564282</t>
+          <t>475182; 565293</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>413756; 495385</t>
+          <t>410777; 498115</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>296021; 372666</t>
+          <t>296479; 374582</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>378733; 484010</t>
+          <t>440094; 513254</t>
         </is>
       </c>
     </row>
